--- a/data/trans_dic/Predimed_R2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/Predimed_R2-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con una adherencia baja a la dieta mediterránea</t>
+          <t>Población con una adherencia baja a la dieta mediterránea (tasa de respuesta: 94,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>87,43; 97,11</t>
+          <t>87,54; 97,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>81,26; 91,99</t>
+          <t>81,5; 92,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86,69; 93,9</t>
+          <t>86,27; 93,88</t>
         </is>
       </c>
     </row>
@@ -627,12 +627,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>81,49; 91,24</t>
+          <t>82,0; 92,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82,33; 89,33</t>
+          <t>82,24; 89,34</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>76,53; 84,55</t>
+          <t>77,57; 84,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>79,46; 85,14</t>
+          <t>79,09; 84,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>79,32; 83,9</t>
+          <t>79,24; 83,98</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>81,51; 94,4</t>
+          <t>81,79; 94,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>61,91; 79,59</t>
+          <t>61,3; 79,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76,49; 88,42</t>
+          <t>76,05; 88,87</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>77,52; 83,98</t>
+          <t>77,74; 84,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>77,3; 82,69</t>
+          <t>77,69; 82,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>78,25; 82,38</t>
+          <t>78,34; 82,52</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>71,05; 78,42</t>
+          <t>70,64; 78,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>73,29; 93,72</t>
+          <t>73,41; 93,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>73,7; 90,09</t>
+          <t>73,65; 89,89</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>77,14; 85,3</t>
+          <t>77,32; 85,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>79,99; 85,35</t>
+          <t>79,86; 85,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>79,98; 84,47</t>
+          <t>80,02; 84,64</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>82,11; 87,88</t>
+          <t>82,05; 87,71</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>78,97; 85,12</t>
+          <t>79,16; 85,12</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>81,06; 85,18</t>
+          <t>81,18; 85,25</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con una adherencia baja a la dieta mediterránea</t>
+          <t>Población con una adherencia baja a la dieta mediterránea (tasa de respuesta: 94,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>301197; 334520</t>
+          <t>301554; 334332</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>226669; 256591</t>
+          <t>227313; 256715</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>540423; 585365</t>
+          <t>537839; 585285</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>321355; 361846</t>
+          <t>321328; 361820</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>392771; 439764</t>
+          <t>395204; 444684</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>729498; 791479</t>
+          <t>728680; 791561</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>389432; 430228</t>
+          <t>394750; 432054</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>411096; 440518</t>
+          <t>409230; 439193</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>814033; 861030</t>
+          <t>813256; 861817</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>693517; 803130</t>
+          <t>695869; 805179</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>423464; 544395</t>
+          <t>419290; 542661</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1173953; 1357084</t>
+          <t>1167145; 1363985</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>405254; 438995</t>
+          <t>406408; 442120</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>402265; 430319</t>
+          <t>404326; 430286</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>816320; 859426</t>
+          <t>817277; 860871</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>241257; 266289</t>
+          <t>239878; 266865</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>434092; 555053</t>
+          <t>434760; 555020</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>686726; 839458</t>
+          <t>686320; 837578</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>197328; 218197</t>
+          <t>197793; 217661</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>309370; 330101</t>
+          <t>308855; 330964</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>513918; 542769</t>
+          <t>514177; 543864</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2649186; 2835376</t>
+          <t>2647321; 2829739</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2733822; 2946526</t>
+          <t>2740215; 2946594</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5421362; 5697167</t>
+          <t>5429194; 5701654</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Predimed_R2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/Predimed_R2-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,21%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>87,54; 97,05</t>
+          <t>87,59; 97,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>81,5; 92,04</t>
+          <t>80,7; 91,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86,27; 93,88</t>
+          <t>86,37; 93,11</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>84,08%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>79,53; 89,55</t>
+          <t>79,13; 88,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>82,0; 92,26</t>
+          <t>79,99; 87,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82,24; 89,34</t>
+          <t>80,79; 86,77</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>82,05%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>77,57; 84,91</t>
+          <t>78,09; 85,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>79,09; 84,89</t>
+          <t>79,6; 84,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>79,24; 83,98</t>
+          <t>79,82; 84,17</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>80,77%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>81,79; 94,64</t>
+          <t>79,01; 85,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>61,3; 79,34</t>
+          <t>76,75; 81,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76,05; 88,87</t>
+          <t>78,81; 82,58</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,49%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>77,74; 84,57</t>
+          <t>77,28; 83,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>77,69; 82,68</t>
+          <t>77,57; 82,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>78,34; 82,52</t>
+          <t>78,21; 82,43</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>74,25%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>70,64; 78,59</t>
+          <t>70,04; 77,47</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>73,41; 93,71</t>
+          <t>71,54; 77,45</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>73,65; 89,89</t>
+          <t>71,63; 76,48</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,11%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>77,32; 85,09</t>
+          <t>77,54; 85,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>79,86; 85,57</t>
+          <t>79,44; 85,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>80,02; 84,64</t>
+          <t>79,88; 84,49</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>81,71%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>82,05; 87,71</t>
+          <t>80,74; 83,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>79,16; 85,12</t>
+          <t>79,84; 82,18</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>81,18; 85,25</t>
+          <t>80,7; 82,69</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>322145</t>
+          <t>330938</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>244072</t>
+          <t>283002</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>566217</t>
+          <t>613940</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>301554; 334332</t>
+          <t>310073; 343419</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>227313; 256715</t>
+          <t>263563; 297703</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>537839; 585285</t>
+          <t>587829; 633687</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>342593</t>
+          <t>379392</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>415183</t>
+          <t>391125</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>757775</t>
+          <t>770517</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>321328; 361820</t>
+          <t>357793; 398882</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>395204; 444684</t>
+          <t>371358; 407191</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>728680; 791561</t>
+          <t>740368; 795171</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>413197</t>
+          <t>480153</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>425696</t>
+          <t>487338</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>838893</t>
+          <t>967491</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>394750; 432054</t>
+          <t>458440; 499522</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>409230; 439193</t>
+          <t>471239; 502411</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>813256; 861817</t>
+          <t>941092; 992457</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>745815</t>
+          <t>544084</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>510638</t>
+          <t>559477</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1256454</t>
+          <t>1103561</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>695869; 805179</t>
+          <t>521510; 561898</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>419290; 542661</t>
+          <t>542060; 577143</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1167145; 1363985</t>
+          <t>1076743; 1128293</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>422981</t>
+          <t>458927</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>417616</t>
+          <t>464145</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>840597</t>
+          <t>923073</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>406408; 442120</t>
+          <t>439073; 476026</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>404326; 430286</t>
+          <t>448914; 478177</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>817277; 860871</t>
+          <t>897007; 945330</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>254216</t>
+          <t>278031</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>492504</t>
+          <t>313826</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>746721</t>
+          <t>591856</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>239878; 266865</t>
+          <t>263345; 291279</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>434760; 555020</t>
+          <t>301272; 326177</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>686320; 837578</t>
+          <t>570955; 609617</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>208896</t>
+          <t>228291</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>320700</t>
+          <t>348454</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>529596</t>
+          <t>576744</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>197793; 217661</t>
+          <t>216972; 238526</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>308855; 330964</t>
+          <t>335676; 360179</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>514177; 543864</t>
+          <t>561046; 593477</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2709843</t>
+          <t>2699816</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2826408</t>
+          <t>2847367</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5536252</t>
+          <t>5547183</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2647321; 2829739</t>
+          <t>2645926; 2743604</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2740215; 2946594</t>
+          <t>2803606; 2885880</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5429194; 5701654</t>
+          <t>5478334; 5613500</t>
         </is>
       </c>
     </row>
